--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -509,10 +509,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-valid-system-local-prescriptionID:jp-core-0002:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {exists(system.substring(0,31) = 'urn:oid:1.2.392.100495.20.3.11.').not() or exists(system.substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$')).not()}</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -526,24 +522,6 @@
   </si>
   <si>
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -565,9 +543,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
@@ -584,9 +559,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.use</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
@@ -615,9 +587,6 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -654,16 +623,13 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.system</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -672,31 +638,29 @@
     <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
-  </si>
-  <si>
     <t>Identifier.system</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$')}</t>
+  </si>
+  <si>
     <t>II.root or Role.id.root</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.value</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -706,9 +670,6 @@
   </si>
   <si>
     <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -733,9 +694,6 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.assigner</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
@@ -761,6 +719,63 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.system</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.value</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.assigner</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier:requestIdentifier</t>
   </si>
   <si>
@@ -791,25 +806,10 @@
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>identifier値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
     <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.period</t>
@@ -2357,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO102"/>
+  <dimension ref="A1:AO110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3675,40 +3675,38 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>91</v>
@@ -3723,17 +3721,15 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3782,34 +3778,34 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -3817,18 +3813,18 @@
         <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3840,15 +3836,17 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3885,31 +3883,31 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
@@ -3918,7 +3916,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3929,44 +3927,46 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3990,43 +3990,43 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4035,21 +4035,21 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4066,25 +4066,25 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4109,13 +4109,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4133,7 +4133,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4154,21 +4154,21 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4191,7 +4191,7 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>193</v>
@@ -4228,66 +4228,66 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AK16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4310,26 +4310,24 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4371,7 +4369,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4392,21 +4390,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4414,7 +4412,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -4429,17 +4427,15 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4488,7 +4484,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4509,21 +4505,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4546,15 +4542,17 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4603,7 +4601,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4624,29 +4622,31 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
@@ -4658,19 +4658,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4720,13 +4720,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4735,31 +4735,29 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4768,7 +4766,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4780,17 +4778,15 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4839,53 +4835,53 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4897,15 +4893,17 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4942,31 +4940,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4975,7 +4973,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4986,44 +4984,46 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5047,43 +5047,43 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5092,21 +5092,21 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5123,25 +5123,25 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5166,13 +5166,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5190,7 +5190,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5211,21 +5211,21 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
@@ -5248,13 +5248,13 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>195</v>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>82</v>
@@ -5285,31 +5285,31 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5330,21 +5330,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5367,26 +5367,24 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5428,7 +5426,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5449,21 +5447,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5471,7 +5469,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5486,17 +5484,15 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5545,7 +5541,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5566,21 +5562,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5603,15 +5599,17 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5660,7 +5658,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5681,23 +5679,25 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5715,19 +5715,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5777,13 +5777,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5792,31 +5792,29 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>236</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5837,17 +5835,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>258</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5896,53 +5892,53 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5954,15 +5950,17 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5999,31 +5997,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6032,7 +6030,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6043,44 +6041,46 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6104,43 +6104,43 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6149,21 +6149,21 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6180,25 +6180,25 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6223,13 +6223,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6247,7 +6247,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6268,21 +6268,21 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -6305,7 +6305,7 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>193</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6342,31 +6342,31 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6387,21 +6387,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6424,26 +6424,24 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6485,7 +6483,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6506,21 +6504,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6528,7 +6526,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6543,17 +6541,15 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6602,7 +6598,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6623,21 +6619,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6660,15 +6656,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6717,7 +6715,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6738,23 +6736,25 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6772,19 +6772,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6834,13 +6834,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6849,27 +6849,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>236</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>269</v>
+        <v>160</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>91</v>
@@ -6886,23 +6886,21 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>270</v>
+        <v>162</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6927,13 +6925,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6951,10 +6949,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>91</v>
@@ -6963,19 +6961,19 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>277</v>
+        <v>165</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6983,21 +6981,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>166</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7009,16 +7007,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
+        <v>167</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7044,52 +7042,52 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>279</v>
+        <v>170</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>286</v>
+        <v>165</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7100,10 +7098,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7111,7 +7109,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7129,15 +7127,17 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>172</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7161,13 +7161,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>291</v>
+        <v>177</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7185,10 +7185,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>179</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>91</v>
@@ -7200,27 +7200,27 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>294</v>
+        <v>180</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>181</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7231,7 +7231,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7240,21 +7240,23 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7278,11 +7280,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>300</v>
+        <v>189</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7300,13 +7304,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>190</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7318,24 +7322,24 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>302</v>
+        <v>180</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>192</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7343,7 +7347,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7358,24 +7362,26 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>194</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7393,13 +7399,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7417,7 +7423,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>197</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7432,27 +7438,27 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>310</v>
+        <v>199</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>201</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7460,7 +7466,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7469,22 +7475,22 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>161</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>202</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
+        <v>203</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>316</v>
+        <v>204</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7534,7 +7540,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7555,21 +7561,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>317</v>
+        <v>206</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>208</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7592,13 +7598,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>321</v>
+        <v>211</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7649,7 +7655,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>212</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7670,21 +7676,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>268</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>215</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7692,7 +7698,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7707,16 +7713,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>324</v>
+        <v>216</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>217</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>218</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>327</v>
+        <v>219</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7766,10 +7772,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7781,27 +7787,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>221</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>332</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7818,22 +7824,22 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>334</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>270</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>271</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>337</v>
+        <v>272</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7859,13 +7865,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7883,7 +7889,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7898,27 +7904,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>338</v>
+        <v>275</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>339</v>
+        <v>276</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>340</v>
+        <v>277</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>278</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>279</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>279</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7941,16 +7947,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>344</v>
+        <v>182</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>345</v>
+        <v>280</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>346</v>
+        <v>280</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7976,13 +7982,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8000,7 +8006,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>279</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8015,27 +8021,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>348</v>
+        <v>285</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8043,31 +8049,31 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>353</v>
+        <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8093,13 +8099,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8117,13 +8123,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8132,16 +8138,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>358</v>
+        <v>294</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8149,10 +8155,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8160,10 +8166,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8172,18 +8178,20 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>360</v>
+        <v>182</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8208,13 +8216,11 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8232,13 +8238,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8247,27 +8253,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>301</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>365</v>
+        <v>302</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>366</v>
+        <v>295</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8290,16 +8296,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>305</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>356</v>
+        <v>306</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8325,13 +8331,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8349,7 +8355,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8364,16 +8370,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>372</v>
+        <v>309</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8381,10 +8387,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8401,22 +8407,22 @@
         <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>375</v>
+        <v>313</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8466,7 +8472,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8481,16 +8487,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>317</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8498,10 +8504,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>318</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>318</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8524,17 +8530,15 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8559,11 +8563,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8581,7 +8587,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>318</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8596,13 +8602,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>387</v>
+        <v>322</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8613,10 +8619,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>323</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8624,7 +8630,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>91</v>
@@ -8636,19 +8642,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>389</v>
+        <v>324</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
+        <v>326</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8698,10 +8704,10 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>323</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>91</v>
@@ -8713,27 +8719,27 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>393</v>
+        <v>331</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8741,10 +8747,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8753,19 +8759,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>334</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>397</v>
+        <v>337</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8791,13 +8797,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8815,13 +8821,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8830,27 +8836,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>400</v>
+        <v>338</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>401</v>
+        <v>339</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>402</v>
+        <v>340</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>403</v>
+        <v>341</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>404</v>
+        <v>342</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,7 +8867,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8873,16 +8879,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>406</v>
+        <v>344</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>345</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>409</v>
+        <v>347</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8932,13 +8938,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8947,27 +8953,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>410</v>
+        <v>348</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>349</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>352</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>352</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8987,19 +8993,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9049,7 +9055,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>412</v>
+        <v>352</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9064,16 +9070,16 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9081,10 +9087,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9092,10 +9098,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9107,17 +9113,15 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>360</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>420</v>
+        <v>361</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9166,13 +9170,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9181,27 +9185,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>365</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9212,7 +9216,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9224,13 +9228,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>423</v>
+        <v>369</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>371</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>356</v>
@@ -9283,13 +9287,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9298,16 +9302,16 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>427</v>
+        <v>340</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9315,10 +9319,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9338,21 +9342,21 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>149</v>
+        <v>375</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9400,7 +9404,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9415,16 +9419,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>433</v>
+        <v>379</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9432,10 +9436,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>381</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>381</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9455,19 +9459,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>435</v>
+        <v>382</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9495,11 +9499,9 @@
       <c r="X61" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Y61" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>439</v>
+        <v>385</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9517,7 +9519,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>381</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9532,13 +9534,13 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9549,10 +9551,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,7 +9565,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9575,13 +9577,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>442</v>
+        <v>389</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>443</v>
+        <v>390</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>444</v>
+        <v>391</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>356</v>
@@ -9634,13 +9636,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9649,16 +9651,16 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9666,10 +9668,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9692,16 +9694,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>448</v>
+        <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>395</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>396</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>451</v>
+        <v>397</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9727,13 +9729,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9751,7 +9753,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9766,27 +9768,27 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>452</v>
+        <v>400</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>453</v>
+        <v>401</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9809,16 +9811,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>457</v>
+        <v>407</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>408</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9868,7 +9870,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9883,16 +9885,16 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>459</v>
+        <v>411</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9900,10 +9902,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9914,7 +9916,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9923,18 +9925,20 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>413</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>462</v>
+        <v>414</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9983,13 +9987,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -9998,13 +10002,13 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10015,10 +10019,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10029,7 +10033,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10038,18 +10042,20 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10098,19 +10104,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>171</v>
+        <v>419</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10119,7 +10125,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>172</v>
+        <v>418</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10130,10 +10136,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10153,18 +10159,20 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10201,17 +10209,19 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>178</v>
+        <v>422</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10223,16 +10233,16 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10243,14 +10253,12 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>472</v>
+        <v>428</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10259,7 +10267,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10268,19 +10276,21 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>474</v>
+        <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10328,28 +10338,28 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>178</v>
+        <v>428</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10360,14 +10370,12 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>478</v>
+        <v>434</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10388,15 +10396,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>480</v>
+        <v>182</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10421,13 +10431,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10445,19 +10455,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>178</v>
+        <v>434</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10466,7 +10476,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10477,14 +10487,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10497,26 +10507,24 @@
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>137</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10564,7 +10572,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>487</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10576,16 +10584,16 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>134</v>
+        <v>446</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10596,10 +10604,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10610,7 +10618,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10622,16 +10630,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>489</v>
+        <v>449</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10681,13 +10689,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10696,13 +10704,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10713,10 +10721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10727,7 +10735,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10739,15 +10747,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>168</v>
+        <v>456</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>169</v>
+        <v>457</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10796,19 +10806,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>171</v>
+        <v>455</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10817,7 +10827,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>172</v>
+        <v>459</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10828,21 +10838,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10854,17 +10864,15 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>137</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>138</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10913,28 +10921,28 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>178</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -10945,46 +10953,42 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11032,19 +11036,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>487</v>
+        <v>164</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11053,7 +11057,7 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11064,10 +11068,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11078,7 +11082,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11090,17 +11094,15 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>497</v>
+        <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11137,31 +11139,29 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>496</v>
+        <v>170</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>501</v>
+        <v>142</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11170,23 +11170,25 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11195,7 +11197,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11207,17 +11209,15 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11266,19 +11266,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>504</v>
+        <v>170</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11287,7 +11287,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11298,12 +11298,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11324,17 +11326,15 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11383,19 +11383,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>509</v>
+        <v>170</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11404,7 +11404,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11415,45 +11415,45 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>515</v>
+        <v>140</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>516</v>
+        <v>146</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11502,28 +11502,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>518</v>
+        <v>134</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11560,15 +11560,17 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>168</v>
+        <v>461</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>169</v>
+        <v>489</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11617,7 +11619,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>171</v>
+        <v>488</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11629,7 +11631,7 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11638,7 +11640,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>172</v>
+        <v>492</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11649,21 +11651,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11675,17 +11677,15 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11722,31 +11722,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11755,7 +11755,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11766,21 +11766,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11789,19 +11789,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>360</v>
+        <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>522</v>
+        <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>523</v>
+        <v>167</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>524</v>
+        <v>140</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11851,19 +11851,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>525</v>
+        <v>170</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11872,61 +11872,61 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>527</v>
+        <v>165</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>495</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>495</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>360</v>
+        <v>137</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>531</v>
+        <v>486</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" t="s" s="2">
-        <v>533</v>
-      </c>
+      <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
         <v>82</v>
       </c>
@@ -11970,19 +11970,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>534</v>
+        <v>487</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -11991,21 +11991,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>535</v>
+        <v>134</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12028,16 +12028,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>538</v>
+        <v>497</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>539</v>
+        <v>498</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12087,7 +12087,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12096,33 +12096,33 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>103</v>
+        <v>501</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>544</v>
+        <v>503</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12145,13 +12145,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>546</v>
+        <v>506</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>547</v>
+        <v>507</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>500</v>
@@ -12204,7 +12204,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12213,10 +12213,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>501</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12225,21 +12225,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12265,13 +12265,13 @@
         <v>505</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>549</v>
+        <v>510</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>550</v>
+        <v>511</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12321,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12339,10 +12339,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>553</v>
+        <v>508</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12353,10 +12353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>554</v>
+        <v>512</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>554</v>
+        <v>512</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12379,16 +12379,20 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>169</v>
+        <v>513</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12436,7 +12440,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>171</v>
+        <v>512</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12448,16 +12452,16 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>172</v>
+        <v>518</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12468,21 +12472,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12494,17 +12498,15 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12541,31 +12543,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12574,7 +12576,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12585,21 +12587,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>556</v>
+        <v>520</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>556</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12608,23 +12610,21 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>557</v>
+        <v>137</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>558</v>
+        <v>138</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>559</v>
+        <v>167</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12660,31 +12660,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>562</v>
+        <v>170</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12693,21 +12693,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>563</v>
+        <v>165</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>521</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>521</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12724,30 +12724,28 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>360</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q89" t="s" s="2">
-        <v>569</v>
-      </c>
+      <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12767,13 +12765,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12791,7 +12789,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>572</v>
+        <v>525</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12800,7 +12798,7 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>103</v>
@@ -12812,21 +12810,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>573</v>
+        <v>527</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>574</v>
+        <v>528</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12849,24 +12847,26 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>168</v>
+        <v>360</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>576</v>
+        <v>530</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="R90" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12908,7 +12908,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>580</v>
+        <v>534</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12917,7 +12917,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12929,21 +12929,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>581</v>
+        <v>535</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>582</v>
+        <v>536</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>583</v>
+        <v>537</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>583</v>
+        <v>537</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12963,27 +12963,27 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>105</v>
+        <v>538</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>539</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13025,7 +13025,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>588</v>
+        <v>537</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13034,7 +13034,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13043,24 +13043,24 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>590</v>
+        <v>543</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>582</v>
+        <v>544</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>545</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>591</v>
+        <v>545</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13080,29 +13080,27 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>497</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>592</v>
+        <v>546</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>593</v>
+        <v>547</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13144,7 +13142,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>597</v>
+        <v>545</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13153,10 +13151,10 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>501</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13165,21 +13163,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>598</v>
+        <v>502</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>582</v>
+        <v>503</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13202,16 +13200,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>600</v>
+        <v>505</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>601</v>
+        <v>549</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>602</v>
+        <v>550</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>356</v>
+        <v>551</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13261,7 +13259,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13279,13 +13277,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13293,10 +13291,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13319,13 +13317,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>461</v>
+        <v>161</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>605</v>
+        <v>162</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>606</v>
+        <v>163</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13376,7 +13374,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>604</v>
+        <v>164</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13388,16 +13386,16 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13408,21 +13406,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13434,15 +13432,17 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13479,31 +13479,31 @@
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13512,7 +13512,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13523,21 +13523,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13546,21 +13546,23 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>137</v>
+        <v>557</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>138</v>
+        <v>558</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>175</v>
+        <v>559</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13608,19 +13610,19 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>178</v>
+        <v>562</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13629,32 +13631,32 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>172</v>
+        <v>563</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13666,24 +13668,24 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>485</v>
+        <v>566</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>146</v>
+        <v>568</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q97" s="2"/>
+      <c r="Q97" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="R97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13703,13 +13705,13 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -13727,19 +13729,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>487</v>
+        <v>572</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13748,21 +13750,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>134</v>
+        <v>573</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>612</v>
+        <v>575</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>612</v>
+        <v>575</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13770,7 +13772,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>91</v>
@@ -13782,27 +13784,27 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>82</v>
@@ -13820,11 +13822,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13842,10 +13846,10 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>91</v>
@@ -13860,24 +13864,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>616</v>
+        <v>581</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>617</v>
+        <v>582</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>618</v>
+        <v>583</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>618</v>
+        <v>583</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13897,27 +13901,27 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>619</v>
+        <v>584</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -13935,13 +13939,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13959,7 +13963,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13968,7 +13972,7 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -13977,24 +13981,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>625</v>
+        <v>590</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>626</v>
+        <v>582</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>627</v>
+        <v>591</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>627</v>
+        <v>591</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14014,27 +14018,29 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>628</v>
+        <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>629</v>
+        <v>592</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>630</v>
+        <v>593</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14076,7 +14082,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14091,38 +14097,38 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>632</v>
+        <v>598</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>633</v>
+        <v>599</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>633</v>
+        <v>599</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14134,16 +14140,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>635</v>
+        <v>600</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>636</v>
+        <v>601</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>637</v>
+        <v>602</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>638</v>
+        <v>356</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14193,13 +14199,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>633</v>
+        <v>599</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14214,10 +14220,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>639</v>
+        <v>603</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14225,10 +14231,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>640</v>
+        <v>604</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>640</v>
+        <v>604</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14239,7 +14245,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14251,17 +14257,15 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>641</v>
+        <v>461</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>642</v>
+        <v>605</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14310,13 +14314,13 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>640</v>
+        <v>604</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
@@ -14325,18 +14329,952 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y106" s="2"/>
+      <c r="Z106" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK110" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AL110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="AN102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO102" t="s" s="2">
+      <c r="AN110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -509,6 +509,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -522,6 +526,24 @@
   </si>
   <si>
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -543,6 +565,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
@@ -559,6 +584,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.use</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
@@ -587,6 +615,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -623,13 +654,16 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.system</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>identifier値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -638,29 +672,31 @@
     <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
+  </si>
+  <si>
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$')}</t>
-  </si>
-  <si>
     <t>II.root or Role.id.root</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.value</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -670,6 +706,9 @@
   </si>
   <si>
     <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -694,6 +733,9 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.assigner</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
@@ -719,63 +761,6 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.system</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.value</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.assigner</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier:requestIdentifier</t>
   </si>
   <si>
@@ -806,10 +791,25 @@
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
   </si>
   <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.period</t>
@@ -2357,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO110"/>
+  <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3675,38 +3675,40 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>91</v>
@@ -3721,15 +3723,17 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3778,34 +3782,34 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -3813,18 +3817,18 @@
         <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3836,17 +3840,15 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3883,31 +3885,31 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
@@ -3916,7 +3918,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3927,46 +3929,44 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3990,43 +3990,43 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AC14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4035,21 +4035,21 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4066,25 +4066,25 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4109,31 +4109,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4154,21 +4154,21 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4191,7 +4191,7 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>193</v>
@@ -4228,13 +4228,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4252,7 +4252,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4264,7 +4264,7 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4273,21 +4273,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4310,24 +4310,26 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4369,7 +4371,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4390,21 +4392,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4412,7 +4414,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -4427,15 +4429,17 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4484,7 +4488,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4505,21 +4509,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4542,17 +4546,15 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4601,7 +4603,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4622,31 +4624,29 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
@@ -4658,19 +4658,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4720,13 +4720,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4735,29 +4735,31 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>157</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4766,7 +4768,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4778,15 +4780,17 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4835,53 +4839,53 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4893,17 +4897,15 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4940,31 +4942,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4973,7 +4975,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4984,46 +4986,44 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5047,43 +5047,43 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="AC23" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AD23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5092,21 +5092,21 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5123,25 +5123,25 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5166,31 +5166,31 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5211,21 +5211,21 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
@@ -5248,13 +5248,13 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>195</v>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>82</v>
@@ -5285,13 +5285,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5309,7 +5309,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5330,21 +5330,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5367,24 +5367,26 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5426,7 +5428,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5447,21 +5449,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5469,7 +5471,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5484,15 +5486,17 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5541,7 +5545,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5562,21 +5566,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5599,17 +5603,15 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5658,7 +5660,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5679,25 +5681,23 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5715,19 +5715,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5777,13 +5777,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5792,29 +5792,31 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>157</v>
+        <v>235</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5835,15 +5837,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5892,53 +5896,53 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5950,17 +5954,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5997,31 +5999,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6030,7 +6032,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6041,46 +6043,44 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6104,43 +6104,43 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="AC32" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6149,21 +6149,21 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6180,25 +6180,25 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6223,31 +6223,31 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6268,21 +6268,21 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -6305,7 +6305,7 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>193</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6342,13 +6342,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6366,7 +6366,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6387,21 +6387,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6424,24 +6424,26 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6483,7 +6485,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6504,21 +6506,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6526,7 +6528,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6541,15 +6543,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6598,7 +6602,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6619,21 +6623,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6656,17 +6660,15 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6715,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6736,25 +6738,23 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6772,19 +6772,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6834,13 +6834,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6849,27 +6849,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>157</v>
+        <v>235</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>91</v>
@@ -6886,21 +6886,23 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6925,13 +6927,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6949,10 +6951,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>91</v>
@@ -6961,19 +6963,19 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6981,21 +6983,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>166</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7007,16 +7009,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>138</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>140</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7042,52 +7044,52 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>170</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7098,10 +7100,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>171</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7109,7 +7111,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7127,17 +7129,15 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7161,13 +7161,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>177</v>
+        <v>291</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>178</v>
+        <v>292</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7185,10 +7185,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>91</v>
@@ -7200,27 +7200,27 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>180</v>
+        <v>294</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7231,7 +7231,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7240,23 +7240,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7280,13 +7278,11 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>189</v>
+        <v>300</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7304,13 +7300,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7322,24 +7318,24 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>191</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>192</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7347,7 +7343,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7362,26 +7358,24 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7399,13 +7393,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7423,7 +7417,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7438,27 +7432,27 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>201</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7466,7 +7460,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7475,22 +7469,22 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>161</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>203</v>
+        <v>315</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>204</v>
+        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7540,7 +7534,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>205</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7561,21 +7555,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7598,13 +7592,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>209</v>
+        <v>319</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7655,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7676,21 +7670,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>215</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7698,7 +7692,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7713,16 +7707,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>216</v>
+        <v>324</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>217</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>218</v>
+        <v>326</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>219</v>
+        <v>327</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7772,10 +7766,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>220</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7787,27 +7781,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>222</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7824,22 +7818,22 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>111</v>
+        <v>334</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>270</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>271</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7865,13 +7859,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7889,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7904,27 +7898,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>276</v>
+        <v>339</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>277</v>
+        <v>340</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>278</v>
+        <v>341</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7947,16 +7941,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7982,13 +7976,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8006,7 +8000,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8021,27 +8015,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>285</v>
+        <v>348</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>286</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>287</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>287</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8049,31 +8043,31 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>353</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>288</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>289</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>290</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8099,13 +8093,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8123,13 +8117,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>287</v>
+        <v>352</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8138,16 +8132,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8155,10 +8149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8166,10 +8160,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8178,20 +8172,18 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>182</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8216,11 +8208,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8238,13 +8232,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8253,27 +8247,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>295</v>
+        <v>366</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8296,16 +8290,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>369</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>304</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>305</v>
+        <v>371</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8331,13 +8325,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8355,7 +8349,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8370,16 +8364,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8387,10 +8381,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8407,22 +8401,22 @@
         <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8472,7 +8466,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8487,16 +8481,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>317</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8504,10 +8498,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>318</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>318</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8530,15 +8524,17 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>319</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>320</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8563,13 +8559,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8587,7 +8581,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>318</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8602,13 +8596,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8619,10 +8613,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8630,7 +8624,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>91</v>
@@ -8642,19 +8636,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>325</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>326</v>
+        <v>391</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8704,10 +8698,10 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>91</v>
@@ -8719,27 +8713,27 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>330</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8747,10 +8741,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8759,19 +8753,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>334</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8797,13 +8791,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8821,13 +8815,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8836,27 +8830,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>338</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>342</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8867,7 +8861,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8879,16 +8873,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>346</v>
+        <v>408</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8938,13 +8932,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8953,27 +8947,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>349</v>
+        <v>411</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8993,19 +8987,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9055,7 +9049,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9070,16 +9064,16 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9087,10 +9081,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9098,10 +9092,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9113,15 +9107,17 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>360</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9170,13 +9166,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9185,27 +9181,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9216,7 +9212,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9228,13 +9224,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>370</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>371</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>356</v>
@@ -9287,13 +9283,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9302,16 +9298,16 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>340</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9319,10 +9315,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9342,21 +9338,21 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>375</v>
+        <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9404,7 +9400,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9419,16 +9415,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>379</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9436,10 +9432,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9459,19 +9455,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9499,9 +9495,11 @@
       <c r="X61" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Y61" s="2"/>
+      <c r="Y61" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9519,7 +9517,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9534,13 +9532,13 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9551,10 +9549,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9565,7 +9563,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9577,13 +9575,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>356</v>
@@ -9636,13 +9634,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9651,16 +9649,16 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9668,10 +9666,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9694,16 +9692,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>182</v>
+        <v>448</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>395</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>397</v>
+        <v>451</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9729,13 +9727,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9753,7 +9751,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9768,27 +9766,27 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>401</v>
+        <v>453</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9811,16 +9809,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>408</v>
+        <v>457</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>409</v>
+        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9870,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9885,16 +9883,16 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9902,10 +9900,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9916,7 +9914,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9925,20 +9923,18 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9987,13 +9983,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10002,13 +9998,13 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10019,10 +10015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10033,7 +10029,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10042,20 +10038,18 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10104,19 +10098,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>419</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10125,7 +10119,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>418</v>
+        <v>172</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10136,10 +10130,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>469</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10159,20 +10153,18 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>423</v>
+        <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10209,19 +10201,17 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>422</v>
+        <v>178</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10233,16 +10223,16 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10253,12 +10243,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10267,7 +10259,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10276,21 +10268,19 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>149</v>
+        <v>474</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>429</v>
+        <v>475</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>430</v>
+        <v>476</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>431</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10338,28 +10328,28 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10370,12 +10360,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10396,17 +10388,15 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>182</v>
+        <v>480</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10431,13 +10421,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10455,19 +10445,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>434</v>
+        <v>178</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10476,7 +10466,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10487,14 +10477,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10507,24 +10497,26 @@
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10572,7 +10564,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10584,16 +10576,16 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>446</v>
+        <v>134</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10604,10 +10596,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10618,7 +10610,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10630,16 +10622,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>449</v>
+        <v>489</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10689,13 +10681,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10704,13 +10696,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10721,10 +10713,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10735,7 +10727,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10747,17 +10739,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>456</v>
+        <v>168</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>457</v>
+        <v>169</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10806,19 +10796,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>455</v>
+        <v>171</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10827,7 +10817,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>459</v>
+        <v>172</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10838,21 +10828,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10864,15 +10854,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>461</v>
+        <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>462</v>
+        <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10921,28 +10913,28 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>460</v>
+        <v>178</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>465</v>
+        <v>172</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -10953,42 +10945,46 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11036,19 +11032,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>164</v>
+        <v>487</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11057,7 +11053,7 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11068,10 +11064,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11082,7 +11078,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11094,15 +11090,17 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>137</v>
+        <v>497</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11139,29 +11137,31 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>170</v>
+        <v>496</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>501</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11170,25 +11170,23 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11197,7 +11195,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11209,15 +11207,17 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11266,19 +11266,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>170</v>
+        <v>504</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11287,7 +11287,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11298,14 +11298,12 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11326,15 +11324,17 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11383,19 +11383,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>170</v>
+        <v>509</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11404,7 +11404,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11415,45 +11415,45 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>140</v>
+        <v>515</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>146</v>
+        <v>516</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11502,28 +11502,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>134</v>
+        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11560,17 +11560,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>461</v>
+        <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>489</v>
+        <v>169</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11619,7 +11617,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>488</v>
+        <v>171</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11631,7 +11629,7 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11640,7 +11638,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>492</v>
+        <v>172</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11651,21 +11649,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11677,15 +11675,17 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11722,31 +11722,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11755,7 +11755,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11766,21 +11766,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11789,19 +11789,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>137</v>
+        <v>360</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>138</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>167</v>
+        <v>523</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>140</v>
+        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11851,19 +11851,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>170</v>
+        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11872,61 +11872,61 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>165</v>
+        <v>527</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>360</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>485</v>
+        <v>530</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>486</v>
+        <v>531</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
       </c>
@@ -11970,19 +11970,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>487</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -11991,21 +11991,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>134</v>
+        <v>535</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12028,16 +12028,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12087,7 +12087,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12096,33 +12096,33 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>501</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>503</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12145,13 +12145,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>506</v>
+        <v>546</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>507</v>
+        <v>547</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>500</v>
@@ -12204,7 +12204,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12213,10 +12213,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>501</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12225,21 +12225,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12265,13 +12265,13 @@
         <v>505</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>500</v>
+        <v>551</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12321,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12339,10 +12339,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>508</v>
+        <v>553</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12353,10 +12353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12379,20 +12379,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>513</v>
+        <v>169</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12440,7 +12436,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>512</v>
+        <v>171</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12452,16 +12448,16 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>518</v>
+        <v>172</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12472,21 +12468,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12498,15 +12494,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12543,31 +12541,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12576,7 +12574,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12587,21 +12585,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12610,21 +12608,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>137</v>
+        <v>557</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>138</v>
+        <v>558</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>167</v>
+        <v>559</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12660,31 +12660,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>170</v>
+        <v>562</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12693,21 +12693,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>165</v>
+        <v>563</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>521</v>
+        <v>565</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>521</v>
+        <v>565</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12724,28 +12724,30 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>360</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>522</v>
+        <v>566</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12765,13 +12767,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12789,7 +12791,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12798,7 +12800,7 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>103</v>
@@ -12810,21 +12812,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>527</v>
+        <v>573</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>528</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>529</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>529</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12847,26 +12849,24 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>360</v>
+        <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>530</v>
+        <v>576</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>533</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12908,7 +12908,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>534</v>
+        <v>580</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12917,7 +12917,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12929,21 +12929,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>535</v>
+        <v>581</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>536</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>537</v>
+        <v>583</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>537</v>
+        <v>583</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12963,27 +12963,27 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>538</v>
+        <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13025,7 +13025,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>537</v>
+        <v>588</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13034,7 +13034,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13043,24 +13043,24 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>544</v>
+        <v>582</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13080,27 +13080,29 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>497</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>546</v>
+        <v>592</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>547</v>
+        <v>593</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13142,7 +13144,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>545</v>
+        <v>597</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13151,10 +13153,10 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>501</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13163,21 +13165,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>502</v>
+        <v>598</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>503</v>
+        <v>582</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13200,16 +13202,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>505</v>
+        <v>600</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>549</v>
+        <v>601</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>550</v>
+        <v>602</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>551</v>
+        <v>356</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13259,7 +13261,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13277,13 +13279,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>553</v>
+        <v>603</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13291,10 +13293,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13317,13 +13319,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>161</v>
+        <v>461</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>162</v>
+        <v>605</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>163</v>
+        <v>606</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13374,7 +13376,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>164</v>
+        <v>604</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13386,16 +13388,16 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>165</v>
+        <v>608</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13406,21 +13408,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>555</v>
+        <v>609</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>555</v>
+        <v>609</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13432,17 +13434,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13479,31 +13479,31 @@
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13512,7 +13512,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13523,21 +13523,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>556</v>
+        <v>610</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>556</v>
+        <v>610</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13546,23 +13546,21 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>557</v>
+        <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>558</v>
+        <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>559</v>
+        <v>175</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13610,19 +13608,19 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>562</v>
+        <v>178</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13631,32 +13629,32 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>563</v>
+        <v>172</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13668,24 +13666,24 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>566</v>
+        <v>485</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O97" t="s" s="2">
-        <v>568</v>
+        <v>146</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q97" t="s" s="2">
-        <v>569</v>
-      </c>
+      <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13705,13 +13703,13 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -13729,19 +13727,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>572</v>
+        <v>487</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13750,21 +13748,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>573</v>
+        <v>134</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>574</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13772,7 +13770,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>91</v>
@@ -13784,27 +13782,27 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>82</v>
@@ -13822,13 +13820,11 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>615</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13846,10 +13842,10 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>91</v>
@@ -13864,24 +13860,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>581</v>
+        <v>616</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>582</v>
+        <v>617</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>583</v>
+        <v>618</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>583</v>
+        <v>618</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13901,27 +13897,27 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>584</v>
+        <v>619</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -13939,13 +13935,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13963,7 +13959,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>588</v>
+        <v>618</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13972,7 +13968,7 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -13981,24 +13977,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>590</v>
+        <v>625</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>582</v>
+        <v>626</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>591</v>
+        <v>627</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>591</v>
+        <v>627</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14018,29 +14014,27 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>111</v>
+        <v>628</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14082,7 +14076,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14097,38 +14091,38 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>598</v>
+        <v>632</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>599</v>
+        <v>633</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>599</v>
+        <v>633</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14140,16 +14134,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>600</v>
+        <v>635</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>356</v>
+        <v>638</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14199,13 +14193,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>599</v>
+        <v>633</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14220,10 +14214,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>603</v>
+        <v>639</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14231,10 +14225,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14245,7 +14239,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14257,15 +14251,17 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>461</v>
+        <v>641</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14314,13 +14310,13 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
@@ -14329,952 +14325,18 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>82</v>
+        <v>645</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>608</v>
+        <v>646</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y106" s="2"/>
-      <c r="Z106" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -499,7 +499,7 @@
 　- requestIdentifier : 処方オーダに対するID  
 　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
 [invariantで定義される識別子]  
-　- valid-system-local-prescriptionID : 医療機関毎に管理される処方箋に対するID  </t>
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
